--- a/Proyecto/output/idx.xlsx
+++ b/Proyecto/output/idx.xlsx
@@ -429,7 +429,7 @@
         <v>84.19052444894858</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>80.30487804878048</v>
       </c>
       <c r="I2">
         <v>99.98991172761666</v>
@@ -461,7 +461,7 @@
         <v>25.56371928046618</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>80.54268292682927</v>
       </c>
       <c r="I3">
         <v>9.979823455233291</v>
@@ -493,7 +493,7 @@
         <v>67.01292120597923</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>59.25609756097562</v>
       </c>
       <c r="I4">
         <v>11.65447667087011</v>
@@ -525,7 +525,7 @@
         <v>29.03470990625792</v>
       </c>
       <c r="H5">
-        <v>90.42136771816715</v>
+        <v>23.94512195121951</v>
       </c>
       <c r="I5">
         <v>2.62547288776797</v>
@@ -557,7 +557,7 @@
         <v>21.30732201672156</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>57.92682926829268</v>
       </c>
       <c r="I6">
         <v>5.457755359394704</v>
@@ -589,7 +589,7 @@
         <v>8.791487205472512</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>59.45121951219512</v>
       </c>
       <c r="I7">
         <v>3.32156368221942</v>
@@ -621,7 +621,7 @@
         <v>34.43121357993413</v>
       </c>
       <c r="H8">
-        <v>96.91457517844808</v>
+        <v>25.66463414634146</v>
       </c>
       <c r="I8">
         <v>3.003783102143757</v>
@@ -653,7 +653,7 @@
         <v>25.69039777045858</v>
       </c>
       <c r="H9">
-        <v>72.16209993092332</v>
+        <v>19.10975609756098</v>
       </c>
       <c r="I9">
         <v>4.158890290037832</v>
@@ -685,7 +685,7 @@
         <v>41.37319483151761</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>49.03048780487805</v>
       </c>
       <c r="I10">
         <v>36.82723833543506</v>
@@ -717,7 +717,7 @@
         <v>17.1015961489739</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>41.31707317073171</v>
       </c>
       <c r="I11">
         <v>3.722572509457756</v>
@@ -749,7 +749,7 @@
         <v>19.07778059285534</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>49.6219512195122</v>
       </c>
       <c r="I12">
         <v>4.877679697351827</v>
@@ -781,7 +781,7 @@
         <v>19.02710919685838</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>27.26219512195122</v>
       </c>
       <c r="I13">
         <v>2.179066834804539</v>
@@ -813,7 +813,7 @@
         <v>22.24474284266532</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>27.95121951219512</v>
       </c>
       <c r="I14">
         <v>1.939470365699874</v>
@@ -845,7 +845,7 @@
         <v>12.79452748923233</v>
       </c>
       <c r="H15">
-        <v>73.01404559060555</v>
+        <v>19.33536585365853</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>28.37598175829745</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>32.0060975609756</v>
       </c>
       <c r="I16">
         <v>1.493064312736444</v>
@@ -909,7 +909,7 @@
         <v>9.931593615404106</v>
       </c>
       <c r="H17">
-        <v>36.72576559981579</v>
+        <v>9.725609756097562</v>
       </c>
       <c r="I17">
         <v>0.1361916771752835</v>
@@ -941,7 +941,7 @@
         <v>26.45046871041298</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>55.96341463414635</v>
       </c>
       <c r="I18">
         <v>2.66078184110971</v>
@@ -973,7 +973,7 @@
         <v>19.53382315682797</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>60.17073170731708</v>
       </c>
       <c r="I19">
         <v>9.235813366960908</v>
@@ -1005,7 +1005,7 @@
         <v>28.55333164428681</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>55.84146341463414</v>
       </c>
       <c r="I20">
         <v>10.48928121059269</v>
@@ -1037,7 +1037,7 @@
         <v>19.73650874081581</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>42.83536585365854</v>
       </c>
       <c r="I21">
         <v>4.857503152585119</v>
@@ -1069,7 +1069,7 @@
         <v>23.94223460856347</v>
       </c>
       <c r="H22">
-        <v>100</v>
+        <v>35.5</v>
       </c>
       <c r="I22">
         <v>3.377049180327869</v>
@@ -1101,7 +1101,7 @@
         <v>15.50544717506968</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>55.35365853658537</v>
       </c>
       <c r="I23">
         <v>21.47793190416141</v>

--- a/Proyecto/output/idx.xlsx
+++ b/Proyecto/output/idx.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -405,6 +405,11 @@
           <t>pib_per_capita</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>IDTR</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -429,7 +434,7 @@
         <v>84.19052444894858</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>80.30487804878048</v>
       </c>
       <c r="I2">
         <v>99.98991172761666</v>
@@ -461,7 +466,7 @@
         <v>25.56371928046618</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>80.54268292682927</v>
       </c>
       <c r="I3">
         <v>9.979823455233291</v>
@@ -493,7 +498,7 @@
         <v>67.01292120597923</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>59.25609756097562</v>
       </c>
       <c r="I4">
         <v>11.65447667087011</v>
@@ -525,7 +530,7 @@
         <v>29.03470990625792</v>
       </c>
       <c r="H5">
-        <v>90.42136771816715</v>
+        <v>23.94512195121951</v>
       </c>
       <c r="I5">
         <v>2.62547288776797</v>
@@ -557,7 +562,7 @@
         <v>21.30732201672156</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>57.92682926829268</v>
       </c>
       <c r="I6">
         <v>5.457755359394704</v>
@@ -589,7 +594,7 @@
         <v>8.791487205472512</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>59.45121951219512</v>
       </c>
       <c r="I7">
         <v>3.32156368221942</v>
@@ -621,7 +626,7 @@
         <v>34.43121357993413</v>
       </c>
       <c r="H8">
-        <v>96.91457517844808</v>
+        <v>25.66463414634146</v>
       </c>
       <c r="I8">
         <v>3.003783102143757</v>
@@ -653,7 +658,7 @@
         <v>25.69039777045858</v>
       </c>
       <c r="H9">
-        <v>72.16209993092332</v>
+        <v>19.10975609756098</v>
       </c>
       <c r="I9">
         <v>4.158890290037832</v>
@@ -685,7 +690,7 @@
         <v>41.37319483151761</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>49.03048780487805</v>
       </c>
       <c r="I10">
         <v>36.82723833543506</v>
@@ -717,7 +722,7 @@
         <v>17.1015961489739</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>41.31707317073171</v>
       </c>
       <c r="I11">
         <v>3.722572509457756</v>
@@ -749,7 +754,7 @@
         <v>19.07778059285534</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>49.6219512195122</v>
       </c>
       <c r="I12">
         <v>4.877679697351827</v>
@@ -781,7 +786,7 @@
         <v>19.02710919685838</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>27.26219512195122</v>
       </c>
       <c r="I13">
         <v>2.179066834804539</v>
@@ -813,7 +818,7 @@
         <v>22.24474284266532</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>27.95121951219512</v>
       </c>
       <c r="I14">
         <v>1.939470365699874</v>
@@ -845,7 +850,7 @@
         <v>12.79452748923233</v>
       </c>
       <c r="H15">
-        <v>73.01404559060555</v>
+        <v>19.33536585365853</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -877,7 +882,7 @@
         <v>28.37598175829745</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>32.0060975609756</v>
       </c>
       <c r="I16">
         <v>1.493064312736444</v>
@@ -909,7 +914,7 @@
         <v>9.931593615404106</v>
       </c>
       <c r="H17">
-        <v>36.72576559981579</v>
+        <v>9.725609756097562</v>
       </c>
       <c r="I17">
         <v>0.1361916771752835</v>
@@ -941,7 +946,7 @@
         <v>26.45046871041298</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>55.96341463414635</v>
       </c>
       <c r="I18">
         <v>2.66078184110971</v>
@@ -973,7 +978,7 @@
         <v>19.53382315682797</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>60.17073170731708</v>
       </c>
       <c r="I19">
         <v>9.235813366960908</v>
@@ -1005,7 +1010,7 @@
         <v>28.55333164428681</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>55.84146341463414</v>
       </c>
       <c r="I20">
         <v>10.48928121059269</v>
@@ -1037,7 +1042,7 @@
         <v>19.73650874081581</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>42.83536585365854</v>
       </c>
       <c r="I21">
         <v>4.857503152585119</v>
@@ -1069,7 +1074,7 @@
         <v>23.94223460856347</v>
       </c>
       <c r="H22">
-        <v>100</v>
+        <v>35.5</v>
       </c>
       <c r="I22">
         <v>3.377049180327869</v>
@@ -1101,7 +1106,7 @@
         <v>15.50544717506968</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>55.35365853658537</v>
       </c>
       <c r="I23">
         <v>21.47793190416141</v>
